--- a/StructureDefinition-lmdi-substance.xlsx
+++ b/StructureDefinition-lmdi-substance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-substance.xlsx
+++ b/StructureDefinition-lmdi-substance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-substance.xlsx
+++ b/StructureDefinition-lmdi-substance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>En tilpasset profil av Substance for å representere virkestoff, basert på no-basis.</t>
+    <t>En tilpasset profil av Substance for å representere virkestoff, basert på no-basis-Substance.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-lmdi-substance.xlsx
+++ b/StructureDefinition-lmdi-substance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-substance.xlsx
+++ b/StructureDefinition-lmdi-substance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
